--- a/output/full_scan/batch_seq0_2026-09-08.xlsx
+++ b/output/full_scan/batch_seq0_2026-09-08.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8103</v>
+        <v>8358</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>699.8725216488309</v>
+        <v>805.4364087415051</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>119.5</v>
+        <v>520</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>67.05643604152185</v>
+        <v>61.00686391953579</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45.21655818883481</v>
+        <v>25.79932183391716</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.6399414665894877</v>
+        <v>0.1693235151879248</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>1.770961598282765</v>
+        <v>6.761544985795563</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8064</v>
+        <v>8103</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>679.8655424497623</v>
+        <v>699.8725216488309</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>134.5</v>
+        <v>119.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>72.85435182474046</v>
+        <v>67.05643604152185</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>19.10664169691511</v>
+        <v>45.21655818883481</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.84848582906062</v>
+        <v>0.6399414665894877</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>3.907586890050746</v>
+        <v>1.770961598282765</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8227</v>
+        <v>8064</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>660.1509332812285</v>
+        <v>679.8655424497623</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>180</v>
+        <v>134.5</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>63.23870131251469</v>
+        <v>72.85435182474046</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>18.59786586302956</v>
+        <v>19.10664169691511</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>2.035158081477314</v>
+        <v>1.84848582906062</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>2.152276722957679</v>
+        <v>3.907586890050746</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8111</v>
+        <v>8227</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>606.7789301282482</v>
+        <v>660.1509332812285</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>69.5</v>
+        <v>180</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>56.48215702183639</v>
+        <v>63.23870131251469</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>28.44716771158643</v>
+        <v>18.59786586302956</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.4701243093090703</v>
+        <v>2.035158081477314</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.5691836016151308</v>
+        <v>2.152276722957679</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8488</v>
+        <v>8111</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>591.7658037240881</v>
+        <v>606.7789301282482</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>10.35</v>
+        <v>69.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>55.55123877765806</v>
+        <v>56.48215702183639</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>27.4966779732739</v>
+        <v>28.44716771158643</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.507477685831765</v>
+        <v>0.4701243093090703</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.0656033441690969</v>
+        <v>0.5691836016151308</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8093</v>
+        <v>8488</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>584.6789091330654</v>
+        <v>591.7658037240881</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>26.4</v>
+        <v>10.35</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>56.1003146271476</v>
+        <v>55.55123877765806</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>19.77155947589932</v>
+        <v>27.4966779732739</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.4669811032059953</v>
+        <v>0.507477685831765</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>-0.2575543971880927</v>
+        <v>0.0656033441690969</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8423</v>
+        <v>8093</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>564.2763992116448</v>
+        <v>584.6789091330654</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>18.15</v>
+        <v>26.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>58.91203510470825</v>
+        <v>56.1003146271476</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>27.45366544381248</v>
+        <v>19.77155947589932</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.027639921164486</v>
+        <v>0.4669811032059953</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0283416353933076</v>
+        <v>-0.2575543971880927</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8464</v>
+        <v>8423</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>558.0936453133331</v>
+        <v>564.2763992116448</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>371.5</v>
+        <v>18.15</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>50.62484022611485</v>
+        <v>58.91203510470825</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.70266763952072</v>
+        <v>27.45366544381248</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.6173060174809516</v>
+        <v>2.027639921164486</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.6814164288816915</v>
+        <v>0.0283416353933076</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8431</v>
+        <v>8464</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>542.1669346481654</v>
+        <v>558.0936453133331</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>63.3</v>
+        <v>371.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>67.10962762660196</v>
+        <v>50.62484022611485</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>29.39452148622025</v>
+        <v>14.70266763952072</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.016693464816541</v>
+        <v>0.6173060174809516</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.106471022547938</v>
+        <v>-0.6814164288816915</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>9105</v>
+        <v>8431</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>536.2569537320483</v>
+        <v>542.1669346481654</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>8.68</v>
+        <v>63.3</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>54.61199241222656</v>
+        <v>67.10962762660196</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>20.37509397187164</v>
+        <v>29.39452148622025</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.320239959802565</v>
+        <v>2.016693464816541</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.0439598439061062</v>
+        <v>2.106471022547938</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8482</v>
+        <v>9105</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>534.5817978395382</v>
+        <v>536.2569537320483</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>49.6</v>
+        <v>8.68</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>52.65650534728008</v>
+        <v>54.61199241222656</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3.393481947481069</v>
+        <v>20.37509397187164</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.4779018474223829</v>
+        <v>1.320239959802565</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.0224323494624794</v>
+        <v>0.0439598439061062</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8926</v>
+        <v>8482</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>533.518833502804</v>
+        <v>534.5817978395382</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>57.2</v>
+        <v>49.6</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>43.73830067409338</v>
+        <v>52.65650534728008</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>27.56251839482455</v>
+        <v>3.393481947481069</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.7795720037560626</v>
+        <v>0.4779018474223829</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.515759078999487</v>
+        <v>0.0224323494624794</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8085</v>
+        <v>8926</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>517.1773909061451</v>
+        <v>533.518833502804</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15.15</v>
+        <v>57.2</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>65.32193718638187</v>
+        <v>43.73830067409338</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>29.65319874898705</v>
+        <v>27.56251839482455</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.3309239562193945</v>
+        <v>0.7795720037560626</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0775660688768588</v>
+        <v>0.515759078999487</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8299</v>
+        <v>8085</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>516.9170149409387</v>
+        <v>517.1773909061451</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2085</v>
+        <v>15.15</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>51.85213494796733</v>
+        <v>65.32193718638187</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>10.11047071166129</v>
+        <v>29.65319874898705</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.4886567926302461</v>
+        <v>0.3309239562193945</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-5.158105021549005</v>
+        <v>0.0775660688768588</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8155</v>
+        <v>8299</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>507.4324496492798</v>
+        <v>516.9170149409387</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>341.5</v>
+        <v>2085</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.09746904876502</v>
+        <v>51.85213494796733</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>19.83375291244417</v>
+        <v>10.11047071166129</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.6325362119127057</v>
+        <v>0.4886567926302461</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.3797969678809707</v>
+        <v>-5.158105021549005</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>9912</v>
+        <v>8155</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>505.1378220975636</v>
+        <v>507.4324496492798</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12.8</v>
+        <v>341.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.1121047902092</v>
+        <v>52.09746904876502</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>22.85863376274303</v>
+        <v>19.83375291244417</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3967085821094819</v>
+        <v>0.6325362119127057</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.032323595930951</v>
+        <v>0.3797969678809707</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8109</v>
+        <v>9912</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>470.145535369488</v>
+        <v>505.1378220975636</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>128.5</v>
+        <v>12.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,49 +1400,49 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46.93030202448907</v>
+        <v>49.1121047902092</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>20.52484990361439</v>
+        <v>22.85863376274303</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.3050857856405592</v>
+        <v>0.3967085821094819</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.3232098828920485</v>
+        <v>-0.032323595930951</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8462</v>
+        <v>8109</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>461.576185105736</v>
+        <v>470.145535369488</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>167</v>
+        <v>128.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>47.39536057057308</v>
+        <v>46.93030202448907</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>26.16875891227361</v>
+        <v>20.52484990361439</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4076474538835535</v>
+        <v>0.3050857856405592</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-1.674187925030941</v>
+        <v>-0.3232098828920485</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8240</v>
+        <v>8462</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>455.536695901856</v>
+        <v>461.576185105736</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>52.3</v>
+        <v>167</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>62.18288938646779</v>
+        <v>47.39536057057308</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>28.9759628699313</v>
+        <v>26.16875891227361</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.353669590185596</v>
+        <v>0.4076474538835535</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.218016611499884</v>
+        <v>-1.674187925030941</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8442</v>
+        <v>8240</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>443.6730335242598</v>
+        <v>455.536695901856</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>46.65</v>
+        <v>52.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>58.32824888288869</v>
+        <v>62.18288938646779</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>15.03109189886432</v>
+        <v>28.9759628699313</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8642061890038766</v>
+        <v>3.353669590185596</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.0655225086295793</v>
+        <v>1.218016611499884</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8147</v>
+        <v>8442</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>439.8642818590379</v>
+        <v>443.6730335242598</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>137</v>
+        <v>46.65</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>59.52293618697017</v>
+        <v>58.32824888288869</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.58859814460314</v>
+        <v>15.03109189886432</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.858801015655359</v>
+        <v>0.8642061890038766</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.272324632090004</v>
+        <v>-0.0655225086295793</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8054</v>
+        <v>8147</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>433.8274584054449</v>
+        <v>439.8642818590379</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>83.3</v>
+        <v>137</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>47.69631894671416</v>
+        <v>59.52293618697017</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>13.23172205316151</v>
+        <v>22.58859814460314</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.096001041314679</v>
+        <v>1.858801015655359</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.6683964424872708</v>
+        <v>2.272324632090004</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8080</v>
+        <v>8054</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>429.121151299915</v>
+        <v>433.8274584054449</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>28.6</v>
+        <v>83.3</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.1318938006681</v>
+        <v>47.69631894671416</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>56.68689901961135</v>
+        <v>13.23172205316151</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5571226907861418</v>
+        <v>2.096001041314679</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0593132664076397</v>
+        <v>0.6683964424872708</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8271</v>
+        <v>8080</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>422.6572673164524</v>
+        <v>429.121151299915</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>219.5</v>
+        <v>28.6</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>46.62462499961641</v>
+        <v>54.1318938006681</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>18.86454817449488</v>
+        <v>56.68689901961135</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4182882872873521</v>
+        <v>0.5571226907861418</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-2.318708769716912</v>
+        <v>0.0593132664076397</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8150</v>
+        <v>8271</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>421.5875787746773</v>
+        <v>422.6572673164524</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>90.3</v>
+        <v>219.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>49.69680602857803</v>
+        <v>46.62462499961641</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>12.40379372688811</v>
+        <v>18.86454817449488</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4891401291685044</v>
+        <v>0.4182882872873521</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.4060358357444777</v>
+        <v>-2.318708769716912</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8367</v>
+        <v>8150</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>420.3664149462224</v>
+        <v>421.5875787746773</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>40.7</v>
+        <v>90.3</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.39627880820115</v>
+        <v>49.69680602857803</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>31.47042960534612</v>
+        <v>12.40379372688811</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.276286505881818</v>
+        <v>0.4891401291685044</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0307755258198077</v>
+        <v>0.4060358357444777</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8043</v>
+        <v>8367</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>414.2599840210683</v>
+        <v>420.3664149462224</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>138</v>
+        <v>40.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>46.93545788972956</v>
+        <v>50.39627880820115</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11.92325090735656</v>
+        <v>31.47042960534612</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.3055397940133592</v>
+        <v>1.276286505881818</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.5883812944127564</v>
+        <v>0.0307755258198077</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8473</v>
+        <v>8043</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>408.2323158695942</v>
+        <v>414.2599840210683</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>39.5</v>
+        <v>138</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>29.9320893912907</v>
+        <v>46.93545788972956</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>27.13812022439832</v>
+        <v>11.92325090735656</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.388484921799864</v>
+        <v>0.3055397940133592</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>-0.3731961174850814</v>
+        <v>0.5883812944127564</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8996</v>
+        <v>8473</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>403.3099385647304</v>
+        <v>408.2323158695942</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1225</v>
+        <v>39.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.63716705843879</v>
+        <v>29.9320893912907</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.78603840686766</v>
+        <v>27.13812022439832</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.127987938223268</v>
+        <v>2.388484921799864</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>3.971003357514178</v>
+        <v>-0.3731961174850814</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8163</v>
+        <v>8996</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>395.9871378961604</v>
+        <v>403.3099385647304</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>30.15</v>
+        <v>1225</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>38.11957600104068</v>
+        <v>52.63716705843879</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>12.79931842647213</v>
+        <v>21.78603840686766</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.576826249177206</v>
+        <v>1.127987938223268</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.0819281084945665</v>
+        <v>3.971003357514178</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8171</v>
+        <v>8163</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>天宇</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>395.8902987248654</v>
+        <v>395.9871378961604</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>19.6</v>
+        <v>30.15</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45.00859520548386</v>
+        <v>38.11957600104068</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>10.91019610524493</v>
+        <v>12.79931842647213</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9183046232442696</v>
+        <v>1.576826249177206</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.001613056365001</v>
+        <v>0.0819281084945665</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8086</v>
+        <v>8171</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>394.5300804111882</v>
+        <v>395.8902987248654</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>110</v>
+        <v>19.6</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>40.93649204918727</v>
+        <v>45.00859520548386</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.42576883806265</v>
+        <v>10.91019610524493</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.4289259433590864</v>
+        <v>0.9183046232442696</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.0323530011447412</v>
+        <v>0.001613056365001</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8289</v>
+        <v>8086</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>387.1472613575128</v>
+        <v>394.5300804111882</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>43.25</v>
+        <v>110</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>40.87324819356159</v>
+        <v>40.93649204918727</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>19.73098803930164</v>
+        <v>17.42576883806265</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6816939867417784</v>
+        <v>0.4289259433590864</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0640520696485319</v>
+        <v>-0.0323530011447412</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>8411</v>
+        <v>8289</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>379.5343780291369</v>
+        <v>387.1472613575128</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>12.8</v>
+        <v>43.25</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.49388494291878</v>
+        <v>40.87324819356159</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15.04945871896529</v>
+        <v>19.73098803930164</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9898756009285008</v>
+        <v>0.6816939867417784</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.009776490869985501</v>
+        <v>-0.0640520696485319</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8069</v>
+        <v>8411</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>379.2273669569853</v>
+        <v>379.5343780291369</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>147</v>
+        <v>12.8</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>32.02697601359191</v>
+        <v>47.49388494291878</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>25.06350827724805</v>
+        <v>15.04945871896529</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6733737878282168</v>
+        <v>0.9898756009285008</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.2419886810564442</v>
+        <v>-0.009776490869985501</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>9103</v>
+        <v>8069</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>376.6384683913615</v>
+        <v>379.2273669569853</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>5.11</v>
+        <v>147</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>47.1404569805207</v>
+        <v>32.02697601359191</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7.65197818766546</v>
+        <v>25.06350827724805</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.5726719236928691</v>
+        <v>0.6733737878282168</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0001486753860862</v>
+        <v>-0.2419886810564442</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8096</v>
+        <v>9103</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>373.5944550141508</v>
+        <v>376.6384683913615</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>101</v>
+        <v>5.11</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>33.99599847297092</v>
+        <v>47.1404569805207</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.77569898797294</v>
+        <v>7.65197818766546</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.7948721026797393</v>
+        <v>0.5726719236928691</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1732746159895244</v>
+        <v>0.0001486753860862</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8182</v>
+        <v>8096</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>371.1151410820274</v>
+        <v>373.5944550141508</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>38.65</v>
+        <v>101</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>43.77630927857343</v>
+        <v>33.99599847297092</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>8.961632553630213</v>
+        <v>21.77569898797294</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.3720955441054337</v>
+        <v>0.7948721026797393</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.0304629873171105</v>
+        <v>0.1732746159895244</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8410</v>
+        <v>8182</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>370.627905261049</v>
+        <v>371.1151410820274</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>29.25</v>
+        <v>38.65</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>28.2216096565059</v>
+        <v>43.77630927857343</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>27.49020945013063</v>
+        <v>8.961632553630213</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.749079012783255</v>
+        <v>0.3720955441054337</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.1623017489284499</v>
+        <v>-0.0304629873171105</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8261</v>
+        <v>8410</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>369.0622229042524</v>
+        <v>370.627905261049</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>170.5</v>
+        <v>29.25</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>40.54588601261324</v>
+        <v>28.2216096565059</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>11.96053329166457</v>
+        <v>27.49020945013063</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.6988070694301253</v>
+        <v>4.749079012783255</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.147452758687326</v>
+        <v>-0.1623017489284499</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8042</v>
+        <v>8261</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>367.4140164627286</v>
+        <v>369.0622229042524</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>113</v>
+        <v>170.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>50.67118525497349</v>
+        <v>40.54588601261324</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>16.64746315136225</v>
+        <v>11.96053329166457</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.959219553884468</v>
+        <v>0.6988070694301253</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>2.676313037695975</v>
+        <v>1.147452758687326</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8105</v>
+        <v>8042</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>361.6550210663201</v>
+        <v>367.4140164627286</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>15.1</v>
+        <v>113</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>42.09686504665203</v>
+        <v>50.67118525497349</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>26.52956886277648</v>
+        <v>16.64746315136225</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.3161635598598792</v>
+        <v>1.959219553884468</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0250792293002866</v>
+        <v>2.676313037695975</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8102</v>
+        <v>8105</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>360.8331349700514</v>
+        <v>361.6550210663201</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>67.2</v>
+        <v>15.1</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>51.19069144815353</v>
+        <v>42.09686504665203</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7.053288012584114</v>
+        <v>26.52956886277648</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3311924171609552</v>
+        <v>0.3161635598598792</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.7203760679187096</v>
+        <v>0.0250792293002866</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8438</v>
+        <v>8102</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>359.8554897190436</v>
+        <v>360.8331349700514</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>68</v>
+        <v>67.2</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>44.76691759182624</v>
+        <v>51.19069144815353</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.64382534670654</v>
+        <v>7.053288012584114</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4722352321987894</v>
+        <v>0.3311924171609552</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.3340162030641669</v>
+        <v>0.7203760679187096</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8481</v>
+        <v>8438</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>353.9499895152616</v>
+        <v>359.8554897190436</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>41.4</v>
+        <v>68</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>56.74032500848772</v>
+        <v>44.76691759182624</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11.31176665495514</v>
+        <v>15.64382534670654</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.7188720363896973</v>
+        <v>0.4722352321987894</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.06627871939511901</v>
+        <v>0.3340162030641669</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8091</v>
+        <v>8481</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>345.0786186240624</v>
+        <v>353.9499895152616</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>213.5</v>
+        <v>41.4</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40.05904509025874</v>
+        <v>56.74032500848772</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.59690728755093</v>
+        <v>11.31176665495514</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.6364891073380525</v>
+        <v>0.7188720363896973</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.5351937110565883</v>
+        <v>0.06627871939511901</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8112</v>
+        <v>8091</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>345.001038972935</v>
+        <v>345.0786186240624</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>89.5</v>
+        <v>213.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.62950734397239</v>
+        <v>40.05904509025874</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>8.800880950968795</v>
+        <v>17.59690728755093</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4717321658153304</v>
+        <v>0.6364891073380525</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.5690345961460513</v>
+        <v>0.5351937110565883</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8472</v>
+        <v>8112</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>337.2811796308156</v>
+        <v>345.001038972935</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>74.2</v>
+        <v>89.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>58.84784206857518</v>
+        <v>46.62950734397239</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.51883471267775</v>
+        <v>8.800880950968795</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.756677169741017</v>
+        <v>0.4717321658153304</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>1.222685837750989</v>
+        <v>-0.5690345961460513</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8074</v>
+        <v>8472</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>332.9304510564038</v>
+        <v>337.2811796308156</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>52.5</v>
+        <v>74.2</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>41.02617830525327</v>
+        <v>58.84784206857518</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>14.70311818455215</v>
+        <v>19.51883471267775</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8991312737664247</v>
+        <v>2.756677169741017</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.08144041389737169</v>
+        <v>1.222685837750989</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8162</v>
+        <v>8074</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>331.2982961666282</v>
+        <v>332.9304510564038</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>61.2</v>
+        <v>52.5</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>50.72258500502829</v>
+        <v>41.02617830525327</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>14.78814511429405</v>
+        <v>14.70311818455215</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.285192002085354</v>
+        <v>0.8991312737664247</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.1233550144066947</v>
+        <v>-0.08144041389737169</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8463</v>
+        <v>8162</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>329.298979919531</v>
+        <v>331.2982961666282</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>21.5</v>
+        <v>61.2</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>56.48752913486992</v>
+        <v>50.72258500502829</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>11.72062358216488</v>
+        <v>14.78814511429405</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.1752751223511406</v>
+        <v>1.285192002085354</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0212976116088188</v>
+        <v>0.1233550144066947</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8131</v>
+        <v>8463</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>328.3609517798315</v>
+        <v>329.298979919531</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>61.9</v>
+        <v>21.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.04717219284139</v>
+        <v>56.48752913486992</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>8.193090213618587</v>
+        <v>11.72062358216488</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.9655258109141828</v>
+        <v>0.1752751223511406</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.1063785256836737</v>
+        <v>0.0212976116088188</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>9802</v>
+        <v>8131</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>325.5382625537314</v>
+        <v>328.3609517798315</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>71.2</v>
+        <v>61.9</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>44.66780460737779</v>
+        <v>46.04717219284139</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>8.611353996514854</v>
+        <v>8.193090213618587</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.403512102691719</v>
+        <v>0.9655258109141828</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.06491908954737351</v>
+        <v>0.1063785256836737</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8443</v>
+        <v>9802</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>317.6552939436281</v>
+        <v>325.5382625537314</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>11.15</v>
+        <v>71.2</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>37.81477113715817</v>
+        <v>44.66780460737779</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>47.62796422656603</v>
+        <v>8.611353996514854</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.102496109752612</v>
+        <v>1.403512102691719</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0232799665593159</v>
+        <v>0.06491908954737351</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>8291</v>
+        <v>8443</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>尚茂</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>312.9173717939337</v>
+        <v>317.6552939436281</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>30</v>
+        <v>11.15</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>38.85658365237408</v>
+        <v>37.81477113715817</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>10.0959018130178</v>
+        <v>47.62796422656603</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.045234977416283</v>
+        <v>0.102496109752612</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.2721389655670776</v>
+        <v>-0.0232799665593159</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>8404</v>
+        <v>8291</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>尚茂</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>312.0300862627205</v>
+        <v>312.9173717939337</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>15.55</v>
+        <v>30</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>31.63836301556</v>
+        <v>38.85658365237408</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>13.47563859934326</v>
+        <v>10.0959018130178</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>3.103008626272048</v>
+        <v>1.045234977416283</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0405775905330251</v>
+        <v>-0.2721389655670776</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>9930</v>
+        <v>8404</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>311.22449361483</v>
+        <v>312.0300862627205</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>62.7</v>
+        <v>15.55</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>43.84361234227867</v>
+        <v>31.63836301556</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>23.06295730745171</v>
+        <v>13.47563859934326</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.9710389789092791</v>
+        <v>3.103008626272048</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.0112388333320385</v>
+        <v>-0.0405775905330251</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8114</v>
+        <v>9930</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>311.1091984112711</v>
+        <v>311.22449361483</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>180</v>
+        <v>62.7</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>35.36519303766292</v>
+        <v>43.84361234227867</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>18.22495108393123</v>
+        <v>23.06295730745171</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.606477673362676</v>
+        <v>0.9710389789092791</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.268239950888602</v>
+        <v>0.0112388333320385</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8374</v>
+        <v>8114</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>308.7152233412305</v>
+        <v>311.1091984112711</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>80.09999999999999</v>
+        <v>180</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>46.60228688048384</v>
+        <v>35.36519303766292</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.35140623781749</v>
+        <v>18.22495108393123</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.7119238631069951</v>
+        <v>2.606477673362676</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.1113231186003143</v>
+        <v>-1.268239950888602</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8092</v>
+        <v>8374</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>302.0654020310905</v>
+        <v>308.7152233412305</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>12.9</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45.02669603112621</v>
+        <v>46.60228688048384</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>14.00165770238024</v>
+        <v>14.35140623781749</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.3870329440917116</v>
+        <v>0.7119238631069951</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.0188388442714623</v>
+        <v>-0.1113231186003143</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8081</v>
+        <v>8092</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>300.3350810529698</v>
+        <v>302.0654020310905</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>248.5</v>
+        <v>12.9</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>41.68973043847046</v>
+        <v>45.02669603112621</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>16.63662768180645</v>
+        <v>14.00165770238024</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.13540056887675</v>
+        <v>0.3870329440917116</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.3763664773915809</v>
+        <v>0.0188388442714623</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8234</v>
+        <v>8081</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>299.6308911001114</v>
+        <v>300.3350810529698</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>66.90000000000001</v>
+        <v>248.5</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.7551857292567</v>
+        <v>41.68973043847046</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15.04494053601016</v>
+        <v>16.63662768180645</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.227814185813252</v>
+        <v>1.13540056887675</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.2261933450418407</v>
+        <v>-0.3763664773915809</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8210</v>
+        <v>8234</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>299.0282972285633</v>
+        <v>299.6308911001114</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>907</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>37.44929144599033</v>
+        <v>48.7551857292567</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>14.61452491165817</v>
+        <v>15.04494053601016</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.557952267733768</v>
+        <v>1.227814185813252</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>1.587830722698669</v>
+        <v>-0.2261933450418407</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8215</v>
+        <v>8210</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>297.3143097450043</v>
+        <v>299.0282972285633</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>25.15</v>
+        <v>907</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>50.40173161559899</v>
+        <v>37.44929144599033</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.23743647843004</v>
+        <v>14.61452491165817</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.7476916756606692</v>
+        <v>1.557952267733768</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.1339117012043822</v>
+        <v>1.587830722698669</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8478</v>
+        <v>8215</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>290.6185205422257</v>
+        <v>297.3143097450043</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>141.5</v>
+        <v>25.15</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>42.98656692152714</v>
+        <v>50.40173161559899</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>9.764172324108022</v>
+        <v>22.23743647843004</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2376659557213829</v>
+        <v>0.7476916756606692</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.327929620729614</v>
+        <v>0.1339117012043822</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8110</v>
+        <v>8478</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>287.8036367232668</v>
+        <v>290.6185205422257</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>43.75</v>
+        <v>141.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>44.30639788548745</v>
+        <v>42.98656692152714</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>8.595523380106535</v>
+        <v>9.764172324108022</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7033800090632368</v>
+        <v>0.2376659557213829</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1161829862910801</v>
+        <v>0.327929620729614</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8101</v>
+        <v>8110</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>282.7830775736664</v>
+        <v>287.8036367232668</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>11.95</v>
+        <v>43.75</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>49.94237845267015</v>
+        <v>44.30639788548745</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>6.112547880780731</v>
+        <v>8.595523380106535</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2496861272865128</v>
+        <v>0.7033800090632368</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0020526549407701</v>
+        <v>-0.1161829862910801</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8046</v>
+        <v>8101</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>279.238379294233</v>
+        <v>282.7830775736664</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>1025</v>
+        <v>11.95</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>40.0051350714391</v>
+        <v>49.94237845267015</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>13.66398575667297</v>
+        <v>6.112547880780731</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4656332896889075</v>
+        <v>0.2496861272865128</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-25.51813935245947</v>
+        <v>-0.0020526549407701</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8183</v>
+        <v>8046</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>275.1109962303807</v>
+        <v>279.238379294233</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>28</v>
+        <v>1025</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>36.9563812181355</v>
+        <v>40.0051350714391</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>24.0941757106308</v>
+        <v>13.66398575667297</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.153539292277283</v>
+        <v>0.4656332896889075</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.074501803124514</v>
+        <v>-25.51813935245947</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>8070</v>
+        <v>8183</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>274.4305098624474</v>
+        <v>275.1109962303807</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>50.58933229621307</v>
+        <v>36.9563812181355</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.94743635967175</v>
+        <v>24.0941757106308</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4775613837023488</v>
+        <v>1.153539292277283</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.014789137639126</v>
+        <v>-0.074501803124514</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8050</v>
+        <v>8070</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>272.9845856717154</v>
+        <v>274.4305098624474</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>55.3</v>
+        <v>50</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>43.60612677852551</v>
+        <v>50.58933229621307</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>10.80530139323997</v>
+        <v>17.94743635967175</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.4102206273901139</v>
+        <v>0.4775613837023488</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.1715013049216598</v>
+        <v>-0.014789137639126</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8390</v>
+        <v>8050</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>272.741631296953</v>
+        <v>272.9845856717154</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>55.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>48.36318489848176</v>
+        <v>43.60612677852551</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10.8965358628052</v>
+        <v>10.80530139323997</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8063899424081644</v>
+        <v>0.4102206273901139</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.1638452550329482</v>
+        <v>-0.1715013049216598</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8104</v>
+        <v>8390</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>271.2025285165109</v>
+        <v>272.741631296953</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>30.1</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>38.07395477146633</v>
+        <v>48.36318489848176</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>21.57340087560823</v>
+        <v>10.8965358628052</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.189528690138721</v>
+        <v>0.8063899424081644</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.08336473192659311</v>
+        <v>-0.1638452550329482</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8072</v>
+        <v>8104</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>270.5764143245936</v>
+        <v>271.2025285165109</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>26.05</v>
+        <v>30.1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>43.12653334435034</v>
+        <v>38.07395477146633</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>20.99475774992929</v>
+        <v>21.57340087560823</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9133518462485646</v>
+        <v>1.189528690138721</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0290042598822273</v>
+        <v>0.08336473192659311</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>9902</v>
+        <v>8072</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>269.8038418778034</v>
+        <v>270.5764143245936</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>13.65</v>
+        <v>26.05</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>47.09400197448554</v>
+        <v>43.12653334435034</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8.268768766961752</v>
+        <v>20.99475774992929</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.9599924236046804</v>
+        <v>0.9133518462485646</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.015293253866613</v>
+        <v>0.0290042598822273</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8383</v>
+        <v>9902</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>269.4015526214728</v>
+        <v>269.8038418778034</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>64.7</v>
+        <v>13.65</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>43.3158085578464</v>
+        <v>47.09400197448554</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>10.24001352491056</v>
+        <v>8.268768766961752</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3929889080097944</v>
+        <v>0.9599924236046804</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0650483449775538</v>
+        <v>-0.015293253866613</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8454</v>
+        <v>8383</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>265.8688972379104</v>
+        <v>269.4015526214728</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>239.5</v>
+        <v>64.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>37.96553253191595</v>
+        <v>43.3158085578464</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.59472893066068</v>
+        <v>10.24001352491056</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.5311522695950337</v>
+        <v>0.3929889080097944</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.9457148803720444</v>
+        <v>-0.0650483449775538</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4608,21 +4608,21 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>9110</v>
+        <v>8454</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>263.8048756676283</v>
+        <v>265.8688972379104</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>2.98</v>
+        <v>239.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.48136516560634</v>
+        <v>37.96553253191595</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>5.954494265114924</v>
+        <v>11.59472893066068</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6233885934211019</v>
+        <v>0.5311522695950337</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0580608294725213</v>
+        <v>-0.9457148803720444</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8076</v>
+        <v>9110</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>262.9379584452763</v>
+        <v>263.8048756676283</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>22</v>
+        <v>2.98</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>33.55233055350367</v>
+        <v>51.48136516560634</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>13.13503605942138</v>
+        <v>5.954494265114924</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.11874572202589</v>
+        <v>0.6233885934211019</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.1194792274910488</v>
+        <v>0.0580608294725213</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8429</v>
+        <v>8076</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>260.5726333557161</v>
+        <v>262.9379584452763</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>5.96</v>
+        <v>22</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.51578781229068</v>
+        <v>33.55233055350367</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7.468965180107815</v>
+        <v>13.13503605942138</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.620607364570355</v>
+        <v>1.11874572202589</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0021271111154396</v>
+        <v>-0.1194792274910488</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8121</v>
+        <v>8429</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>253.5228699872682</v>
+        <v>260.5726333557161</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>27</v>
+        <v>5.96</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>37.33899896430945</v>
+        <v>39.51578781229068</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>26.33106279293974</v>
+        <v>7.468965180107815</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5900557570620765</v>
+        <v>1.620607364570355</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.3104420030765966</v>
+        <v>0.0021271111154396</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8341</v>
+        <v>8121</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>252.1432426627345</v>
+        <v>253.5228699872682</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>27</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>36.22462285865602</v>
+        <v>37.33899896430945</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>9.025733968625405</v>
+        <v>26.33106279293974</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.545756878986694</v>
+        <v>0.5900557570620765</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.1595603158190587</v>
+        <v>0.3104420030765966</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8097</v>
+        <v>8341</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>247.4938907308553</v>
+        <v>252.1432426627345</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>48.55</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>29.41671794097091</v>
+        <v>36.22462285865602</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>31.50176378015682</v>
+        <v>9.025733968625405</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.9275706295267389</v>
+        <v>1.545756878986694</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1021996496443855</v>
+        <v>-0.1595603158190587</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8213</v>
+        <v>8097</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>238.2317000335012</v>
+        <v>247.4938907308553</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>32.55</v>
+        <v>48.55</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>48.11875474825118</v>
+        <v>29.41671794097091</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.5424885566226</v>
+        <v>31.50176378015682</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.6765781559183752</v>
+        <v>0.9275706295267389</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0005997196652008</v>
+        <v>0.1021996496443855</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8071</v>
+        <v>8213</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>237.5939705806832</v>
+        <v>238.2317000335012</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>22.45</v>
+        <v>32.55</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>39.72303292417513</v>
+        <v>48.11875474825118</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.79136578513123</v>
+        <v>17.5424885566226</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.4443775537945603</v>
+        <v>0.6765781559183752</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.1015142494628315</v>
+        <v>0.0005997196652008</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8277</v>
+        <v>8071</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>237.2811233867859</v>
+        <v>237.5939705806832</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>8.08</v>
+        <v>22.45</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.59103236192264</v>
+        <v>39.72303292417513</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>13.88033818423029</v>
+        <v>11.79136578513123</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.971833730934359</v>
+        <v>0.4443775537945603</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0201635028893316</v>
+        <v>-0.1015142494628315</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>9904</v>
+        <v>8277</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>231.875069162628</v>
+        <v>237.2811233867859</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>24.7</v>
+        <v>8.08</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>51.25144156787813</v>
+        <v>48.59103236192264</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.32193067629605</v>
+        <v>13.88033818423029</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4176530582981632</v>
+        <v>1.971833730934359</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0197480889413337</v>
+        <v>0.0201635028893316</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8477</v>
+        <v>9904</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>229.3995621620184</v>
+        <v>231.875069162628</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>15.4</v>
+        <v>24.7</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.34020775968862</v>
+        <v>51.25144156787813</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>7.650760874537728</v>
+        <v>16.32193067629605</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.414556240018252</v>
+        <v>0.4176530582981632</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0331009147501854</v>
+        <v>-0.0197480889413337</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8932</v>
+        <v>8477</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>223.1542489819086</v>
+        <v>229.3995621620184</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>15.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>40.5987241303904</v>
+        <v>49.34020775968862</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>18.04494190395795</v>
+        <v>7.650760874537728</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5629272279731568</v>
+        <v>1.414556240018252</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-1.333665491257931</v>
+        <v>-0.0331009147501854</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8047</v>
+        <v>8932</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>星雲</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>212.9441090986998</v>
+        <v>223.1542489819085</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>42.1</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.82739774960321</v>
+        <v>40.5987241303904</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>10.30762930513796</v>
+        <v>18.04494190395795</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5893161059320287</v>
+        <v>0.5629272279731568</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0549782788641526</v>
+        <v>-1.333665491257931</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8067</v>
+        <v>8047</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>星雲</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>211.90422646043</v>
+        <v>212.9441090986998</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>12.1</v>
+        <v>42.1</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.06797712531439</v>
+        <v>49.82739774960321</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>10.75728893659365</v>
+        <v>10.30762930513796</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.3064941972002203</v>
+        <v>0.5893161059320287</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0480716991351266</v>
+        <v>0.0549782788641526</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8068</v>
+        <v>8067</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>211.0839623895279</v>
+        <v>211.90422646043</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>16.8</v>
+        <v>12.1</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>37.24732392274999</v>
+        <v>44.06797712531439</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>13.9460879718092</v>
+        <v>10.75728893659365</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.2220783331058853</v>
+        <v>0.3064941972002203</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0261041783268787</v>
+        <v>-0.0480716991351266</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8049</v>
+        <v>8068</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>209.36723372393</v>
+        <v>211.0839623895279</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>24.3</v>
+        <v>16.8</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>32.50633356116342</v>
+        <v>37.24732392274999</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>23.82978260038692</v>
+        <v>13.9460879718092</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.038580943475518</v>
+        <v>0.2220783331058853</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.01892958512877</v>
+        <v>0.0261041783268787</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8476</v>
+        <v>8049</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>208.4908962111192</v>
+        <v>209.36723372393</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>19.4</v>
+        <v>24.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.87905031059714</v>
+        <v>32.50633356116342</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>12.87226848185232</v>
+        <v>23.82978260038692</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.9138419763282528</v>
+        <v>1.038580943475518</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0071296114653363</v>
+        <v>0.01892958512877</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8176</v>
+        <v>8476</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>208.3116656043548</v>
+        <v>208.4908962111192</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>9.800000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>44.48385646359857</v>
+        <v>42.87905031059714</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>16.48397770998846</v>
+        <v>12.87226848185232</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2864826038692367</v>
+        <v>0.9138419763282528</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0067582404511745</v>
+        <v>-0.0071296114653363</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8466</v>
+        <v>8176</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>204.5337753629566</v>
+        <v>208.3116656043548</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>34.34177758816998</v>
+        <v>44.48385646359857</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>34.00071571861713</v>
+        <v>16.48397770998846</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.2952838089840162</v>
+        <v>0.2864826038692367</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.0395541232955243</v>
+        <v>-0.0067582404511745</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>9955</v>
+        <v>8466</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>202.1037570735376</v>
+        <v>204.5337753629566</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>23.8</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>41.97590443328715</v>
+        <v>34.34177758816998</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15.22666938910292</v>
+        <v>34.00071571861713</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4747270966359032</v>
+        <v>0.2952838089840162</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0794444788295768</v>
+        <v>-0.0395541232955243</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8422</v>
+        <v>9955</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>202.0608605517691</v>
+        <v>202.1037570735376</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>26.6</v>
+        <v>23.8</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.86937502374448</v>
+        <v>41.97590443328715</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>11.93523586154289</v>
+        <v>15.22666938910292</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.9844337850970096</v>
+        <v>0.4747270966359032</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0769287395801891</v>
+        <v>-0.0794444788295768</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>9136</v>
+        <v>8422</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>200.2878001302067</v>
+        <v>202.0608605517691</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>10.45</v>
+        <v>26.6</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>36.02741011360779</v>
+        <v>49.86937502374448</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.855886790246839</v>
+        <v>11.93523586154289</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.5856773522107672</v>
+        <v>0.9844337850970096</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.043747817155743</v>
+        <v>-0.0769287395801891</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8455</v>
+        <v>9136</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>186.9473572374745</v>
+        <v>200.2878001302067</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>22.75</v>
+        <v>10.45</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.70556637363577</v>
+        <v>36.02741011360779</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.86607833662043</v>
+        <v>8.855886790246839</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.197876406880442</v>
+        <v>0.5856773522107672</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.3602088173728019</v>
+        <v>-0.043747817155743</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8048</v>
+        <v>8455</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>183.9150794688341</v>
+        <v>186.9473572374745</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>50</v>
+        <v>22.75</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>39.56123456549776</v>
+        <v>49.70556637363577</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.23077744203323</v>
+        <v>10.86607833662043</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.9961189037359924</v>
+        <v>1.197876406880442</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.0172917214465989</v>
+        <v>0.3602088173728019</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8222</v>
+        <v>8048</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>176.307720114777</v>
+        <v>183.9150794688341</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>36.45</v>
+        <v>50</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.08857177208703</v>
+        <v>39.56123456549776</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>19.2696300575773</v>
+        <v>13.23077744203323</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.2960598614254544</v>
+        <v>0.9961189037359924</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.3892949289757462</v>
+        <v>0.0172917214465989</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8087</v>
+        <v>8222</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>173.757036562632</v>
+        <v>176.307720114777</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>0</v>
+        <v>36.45</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>22.28543271930324</v>
+        <v>40.08857177208703</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.19367259645867</v>
+        <v>19.2696300575773</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>8.987572434216587e-05</v>
+        <v>0.2960598614254544</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-2.627245668502905</v>
+        <v>-0.3892949289757462</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5986,21 +5986,21 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8084</v>
+        <v>8087</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>173.6152070636529</v>
+        <v>173.757036562632</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>45.3</v>
+        <v>0</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>43.40117835366166</v>
+        <v>22.28543271930324</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.66409338079107</v>
+        <v>13.19367259645867</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.261520706365289</v>
+        <v>8.987572434216587e-05</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.3735654547904689</v>
+        <v>-2.627245668502905</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8201</v>
+        <v>8084</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>173.0349680992333</v>
+        <v>173.6152070636529</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>11.55</v>
+        <v>45.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.13512398460762</v>
+        <v>43.40117835366166</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.67156862493267</v>
+        <v>13.66409338079107</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.4848122590933003</v>
+        <v>1.261520706365289</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0047167616141468</v>
+        <v>-0.3735654547904689</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8249</v>
+        <v>8201</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>166.2241559387943</v>
+        <v>173.0349680992333</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>39.75</v>
+        <v>11.55</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.90649381960394</v>
+        <v>39.13512398460762</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>19.10566478277701</v>
+        <v>16.67156862493267</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.7027781394987046</v>
+        <v>0.4848122590933003</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0708114687033036</v>
+        <v>-0.0047167616141468</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8088</v>
+        <v>8249</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>164.9328995678983</v>
+        <v>166.2241559387943</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>43.2</v>
+        <v>39.75</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>35.50376938332954</v>
+        <v>39.90649381960394</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.06638930097594</v>
+        <v>19.10566478277701</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.7118249132423697</v>
+        <v>0.7027781394987046</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.06262949784433661</v>
+        <v>0.0708114687033036</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6198,21 +6198,21 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8059</v>
+        <v>8088</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>153.3686127295695</v>
+        <v>164.9328995678983</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>13.4</v>
+        <v>43.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>39.90437597601967</v>
+        <v>35.50376938332954</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>17.97554866251921</v>
+        <v>13.06638930097594</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.6056588768288415</v>
+        <v>0.7118249132423697</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.0405598251750031</v>
+        <v>-0.06262949784433661</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8440</v>
+        <v>8059</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>152.7751849879036</v>
+        <v>153.3686127295695</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>20</v>
+        <v>13.4</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.62534283399542</v>
+        <v>39.90437597601967</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.23368256849745</v>
+        <v>17.97554866251921</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.6056793688452797</v>
+        <v>0.6056588768288415</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0212693446795234</v>
+        <v>0.0405598251750031</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8499</v>
+        <v>8440</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>148.5065665627439</v>
+        <v>152.7751849879036</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>257</v>
+        <v>20</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>45.44414425136486</v>
+        <v>44.62534283399542</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>10.38757509164116</v>
+        <v>18.23368256849745</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.574268308441523</v>
+        <v>0.6056793688452797</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.7906062392472926</v>
+        <v>-0.0212693446795234</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8487</v>
+        <v>8499</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>148.4660231485485</v>
+        <v>148.5065665627439</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>71.3</v>
+        <v>257</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.27251763194593</v>
+        <v>45.44414425136486</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.04226583814055</v>
+        <v>10.38757509164116</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.4880715437890028</v>
+        <v>0.574268308441523</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.19177991957834</v>
+        <v>-0.7906062392472926</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8940</v>
+        <v>8487</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>144.3128997713586</v>
+        <v>148.4660231485485</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>14.85</v>
+        <v>71.3</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.26830903711048</v>
+        <v>43.27251763194593</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>11.20114692412512</v>
+        <v>13.04226583814055</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3969132143774629</v>
+        <v>0.4880715437890028</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0157241555423975</v>
+        <v>0.19177991957834</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8467</v>
+        <v>8940</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>143.0219692519363</v>
+        <v>144.3128997713586</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>14.85</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>34.68335802248372</v>
+        <v>35.26830903711048</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>10.97125105373515</v>
+        <v>11.20114692412512</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5017097254580456</v>
+        <v>0.3969132143774629</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0647982536520932</v>
+        <v>-0.0157241555423975</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8044</v>
+        <v>8467</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>135.7570039241131</v>
+        <v>143.0219692519363</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>23.55</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>30.17198662539336</v>
+        <v>34.68335802248372</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.46078187112411</v>
+        <v>10.97125105373515</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7406788483537403</v>
+        <v>0.5017097254580456</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.0844150881963078</v>
+        <v>-0.0647982536520932</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8045</v>
+        <v>8044</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>達運光電</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>131.7223276609471</v>
+        <v>135.7570039241131</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>48.9</v>
+        <v>23.55</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>36.82329031329712</v>
+        <v>30.17198662539336</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14.14903431635372</v>
+        <v>16.46078187112411</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.6155740694191919</v>
+        <v>0.7406788483537403</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.0484805015897047</v>
+        <v>-0.0844150881963078</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,52 +6622,105 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
+        <v>8045</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>達運光電</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>131.7223276609471</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>36.82329031329712</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>14.14903431635372</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.6155740694191919</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.0484805015897047</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>8089</v>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>康全電訊</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>121.1136066118542</v>
       </c>
-      <c r="E117" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>16.9</v>
       </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>33.05542880533274</v>
       </c>
-      <c r="I117" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>13.80883359924396</v>
       </c>
-      <c r="J117" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>1.114998884611916</v>
       </c>
-      <c r="K117" s="2" t="n">
+      <c r="K118" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>-0.0537397996739998</v>
       </c>
-      <c r="O117" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
